--- a/stories/historystory/历朝末年人物事件清单/历朝历代末年风云人物与事件汇总表 .xlsx
+++ b/stories/historystory/历朝末年人物事件清单/历朝历代末年风云人物与事件汇总表 .xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>https://www.qulishi.com/renwu/jie/</t>
+          <t>https://baike.baidu.com/item/桀/67800</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
@@ -582,7 +582,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>• 《史记·夏本纪》: https://www.zgbk.com/char_1958581.html
+          <t>• 《史记·夏本纪》: https://baike.baidu.com/item/夏本纪
 • 《竹书纪年》: https://baike.baidu.com/item/竹书纪年
 • 《列女传》: https://baike.baidu.com/item/列女传
 • 百度百科：夏桀: https://baike.baidu.com/item/桀
@@ -593,7 +593,7 @@
         <is>
           <t>• 《竹书纪年·夏纪》: https://baike.baidu.com/item/竹书纪年
 • 《列女传·孽嬖传·夏桀妹喜》: https://baike.baidu.com/item/列女传
-• 百度百科：倾宫: https://baike.baidu.com/item/倾宫</t>
+• 百度百科：倾宫: https://baike.baidu.com/item/瑶台</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>https://www.qulishi.com/renwu/jie/</t>
+          <t>https://baike.baidu.com/item/桀/67800</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
@@ -634,7 +634,7 @@
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>• 《史记·夏本纪》: https://www.zgbk.com/char_1958581.html
+          <t>• 《史记·夏本纪》: https://baike.baidu.com/item/夏本纪
 • 《竹书纪年》: https://baike.baidu.com/item/竹书纪年
 • 《列女传》: https://baike.baidu.com/item/列女传
 • 百度百科：夏桀: https://baike.baidu.com/item/桀
@@ -668,7 +668,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>https://www.qulishi.com/renwu/jie/</t>
+          <t>https://baike.baidu.com/item/桀/67800</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -686,7 +686,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>• 《史记·夏本纪》: https://www.zgbk.com/char_1958581.html
+          <t>• 《史记·夏本纪》: https://baike.baidu.com/item/夏本纪
 • 《竹书纪年》: https://baike.baidu.com/item/竹书纪年
 • 《列女传》: https://baike.baidu.com/item/列女传
 • 百度百科：夏桀: https://baike.baidu.com/item/桀
@@ -722,7 +722,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>https://www.qulishi.com/renwu/jie/</t>
+          <t>https://baike.baidu.com/item/桀/67800</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
@@ -740,7 +740,7 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>• 《史记·夏本纪》: https://www.zgbk.com/char_1958581.html
+          <t>• 《史记·夏本纪》: https://baike.baidu.com/item/夏本纪
 • 《竹书纪年》: https://baike.baidu.com/item/竹书纪年
 • 《列女传》: https://baike.baidu.com/item/列女传
 • 百度百科：夏桀: https://baike.baidu.com/item/桀
@@ -749,8 +749,8 @@
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>• 《史记·夏本纪》: https://www.zgbk.com/char_1958581.html
-• 《史记·殷本纪》: https://www.zgbk.com/char_1958582.html
+          <t>• 《史记·夏本纪》: https://baike.baidu.com/item/夏本纪
+• 《史记·殷本纪》: https://baike.baidu.com/item/殷本纪
 • 百度百科：夏台: https://baike.baidu.com/item/夏台
 • 百度百科：商汤: https://baike.baidu.com/item/商汤</t>
         </is>
@@ -775,7 +775,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>https://www.qulishi.com/renwu/jie/</t>
+          <t>https://baike.baidu.com/item/桀/67800</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -793,7 +793,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>• 《史记·夏本纪》: https://www.zgbk.com/char_1958581.html
+          <t>• 《史记·夏本纪》: https://baike.baidu.com/item/夏本纪
 • 《竹书纪年》: https://baike.baidu.com/item/竹书纪年
 • 《列女传》: https://baike.baidu.com/item/列女传
 • 百度百科：夏桀: https://baike.baidu.com/item/桀
@@ -803,7 +803,7 @@
       <c r="J6" s="4" t="inlineStr">
         <is>
           <t>• 《尚书·汤誓》: https://baike.baidu.com/item/汤誓
-• 《史记·殷本纪》: https://www.zgbk.com/char_1958582.html
+• 《史记·殷本纪》: https://baike.baidu.com/item/殷本纪
 • 百度百科：鸣条之战: https://baike.baidu.com/item/鸣条之战</t>
         </is>
       </c>
@@ -827,7 +827,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>https://www.qulishi.com/renwu/meixi/</t>
+          <t>https://baike.baidu.com/item/妺喜</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
@@ -855,7 +855,7 @@
         <is>
           <t>• 《列女传·孽嬖传》: https://baike.baidu.com/item/列女传
 • 《帝王世纪》: https://baike.baidu.com/item/帝王世纪
-• 百度百科：裂缯: https://baike.baidu.com/item/裂缯</t>
+• 百度百科：裂缯: https://baike.baidu.com/item/妺喜</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>https://www.qulishi.com/renwu/meixi/</t>
+          <t>https://baike.baidu.com/item/妺喜</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -904,7 +904,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>• 《史记·殷本纪》: https://www.zgbk.com/char_1958582.html
+          <t>• 《史记·殷本纪》: https://baike.baidu.com/item/殷本纪
 • 《韩非子·说林》: https://baike.baidu.com/item/韩非子
 • 百度百科：酒池肉林: https://baike.baidu.com/item/酒池肉林</t>
         </is>
@@ -929,7 +929,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>https://www.qulishi.com/renwu/meixi/</t>
+          <t>https://baike.baidu.com/item/妺喜</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>https://www.qulishi.com/renwu/guanlongpang/</t>
+          <t>https://baike.baidu.com/item/关龙逄</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>https://www.qulishi.com/renwu/guanlongpang/</t>
+          <t>https://baike.baidu.com/item/关龙逄</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
@@ -1055,8 +1055,8 @@
       <c r="J11" s="6" t="inlineStr">
         <is>
           <t>• 《吕氏春秋·必己》: https://baike.baidu.com/item/吕氏春秋
-• 《史记·夏本纪》: https://www.zgbk.com/char_1958581.html
-• 百度百科：炮烙: https://baike.baidu.com/item/炮烙</t>
+• 《史记·夏本纪》: https://baike.baidu.com/item/夏本纪
+• 百度百科：炮烙: https://baike.baidu.com/item/炮烙之刑</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>https://www.qulishi.com/renwu/yiyin/</t>
+          <t>https://baike.baidu.com/item/伊尹</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>• 《史记·殷本纪》: https://www.zgbk.com/char_1958582.html
+          <t>• 《史记·殷本纪》: https://baike.baidu.com/item/殷本纪
 • 《吕氏春秋·本味》: https://baike.baidu.com/item/吕氏春秋
 • 百度百科：伊尹: https://baike.baidu.com/item/伊尹</t>
         </is>
@@ -1105,8 +1105,8 @@
       <c r="J12" s="4" t="inlineStr">
         <is>
           <t>• 《吕氏春秋·本味》: https://baike.baidu.com/item/吕氏春秋
-• 《史记·殷本纪》: https://www.zgbk.com/char_1958582.html
-• 百度百科：负鼎俎: https://baike.baidu.com/item/负鼎俎</t>
+• 《史记·殷本纪》: https://baike.baidu.com/item/殷本纪
+• 百度百科：负鼎俎: https://baike.baidu.com/item/伊尹</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>https://www.qulishi.com/renwu/yiyin/</t>
+          <t>https://baike.baidu.com/item/伊尹</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>• 《史记·殷本纪》: https://www.zgbk.com/char_1958582.html
+          <t>• 《史记·殷本纪》: https://baike.baidu.com/item/殷本纪
 • 《吕氏春秋·本味》: https://baike.baidu.com/item/吕氏春秋
 • 百度百科：伊尹: https://baike.baidu.com/item/伊尹</t>
         </is>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>https://www.qulishi.com/renwu/yiyin/</t>
+          <t>https://baike.baidu.com/item/伊尹</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -1197,14 +1197,14 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>• 《史记·殷本纪》: https://www.zgbk.com/char_1958582.html
+          <t>• 《史记·殷本纪》: https://baike.baidu.com/item/殷本纪
 • 《吕氏春秋·本味》: https://baike.baidu.com/item/吕氏春秋
 • 百度百科：伊尹: https://baike.baidu.com/item/伊尹</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>• 《史记·殷本纪》: https://www.zgbk.com/char_1958582.html
+          <t>• 《史记·殷本纪》: https://baike.baidu.com/item/殷本纪
 • 《孟子·万章上》: https://baike.baidu.com/item/孟子
 • 百度百科：伊尹放太甲: https://baike.baidu.com/item/伊尹放太甲</t>
         </is>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>https://www.qulishi.com/renwu/yiyin/</t>
+          <t>https://baike.baidu.com/item/伊尹</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
@@ -1247,14 +1247,14 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>• 《史记·殷本纪》: https://www.zgbk.com/char_1958582.html
+          <t>• 《史记·殷本纪》: https://baike.baidu.com/item/殷本纪
 • 《吕氏春秋·本味》: https://baike.baidu.com/item/吕氏春秋
 • 百度百科：伊尹: https://baike.baidu.com/item/伊尹</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>• 《史记·殷本纪》: https://www.zgbk.com/char_1958582.html
+          <t>• 《史记·殷本纪》: https://baike.baidu.com/item/殷本纪
 • 《孟子·万章上》: https://baike.baidu.com/item/孟子
 • 百度百科：伊尹放太甲: https://baike.baidu.com/item/伊尹放太甲</t>
         </is>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>https://www.qulishi.com/renwu/tang/</t>
+          <t>https://baike.baidu.com/item/商汤</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -1297,14 +1297,14 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>• 《史记·殷本纪》: https://www.zgbk.com/char_1958582.html
+          <t>• 《史记·殷本纪》: https://baike.baidu.com/item/殷本纪
 • 《尚书·汤誓》: https://baike.baidu.com/item/汤誓
 • 百度百科：商汤: https://baike.baidu.com/item/商汤</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>• 《史记·殷本纪》: https://www.zgbk.com/char_1958582.html
+          <t>• 《史记·殷本纪》: https://baike.baidu.com/item/殷本纪
 • 《吕氏春秋·异用》: https://baike.baidu.com/item/吕氏春秋
 • 百度百科：网开三面: https://baike.baidu.com/item/网开三面</t>
         </is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>https://www.qulishi.com/renwu/tang/</t>
+          <t>https://baike.baidu.com/item/商汤</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>• 《史记·殷本纪》: https://www.zgbk.com/char_1958582.html
+          <t>• 《史记·殷本纪》: https://baike.baidu.com/item/殷本纪
 • 《尚书·汤誓》: https://baike.baidu.com/item/汤誓
 • 百度百科：商汤: https://baike.baidu.com/item/商汤</t>
         </is>
@@ -1355,7 +1355,7 @@
       <c r="J17" s="6" t="inlineStr">
         <is>
           <t>• 《尚书·汤誓》: https://baike.baidu.com/item/汤誓
-• 《史记·殷本纪》: https://www.zgbk.com/char_1958582.html
+• 《史记·殷本纪》: https://baike.baidu.com/item/殷本纪
 • 百度百科：汤誓: https://baike.baidu.com/item/汤誓</t>
         </is>
       </c>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>https://www.qulishi.com/renwu/tang/</t>
+          <t>https://baike.baidu.com/item/商汤</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>• 《史记·殷本纪》: https://www.zgbk.com/char_1958582.html
+          <t>• 《史记·殷本纪》: https://baike.baidu.com/item/殷本纪
 • 《尚书·汤誓》: https://baike.baidu.com/item/汤誓
 • 百度百科：商汤: https://baike.baidu.com/item/商汤</t>
         </is>
@@ -1405,7 +1405,7 @@
       <c r="J18" s="4" t="inlineStr">
         <is>
           <t>• 《尚书·汤誓》: https://baike.baidu.com/item/汤誓
-• 《史记·殷本纪》: https://www.zgbk.com/char_1958582.html
+• 《史记·殷本纪》: https://baike.baidu.com/item/殷本纪
 • 百度百科：鸣条之战: https://baike.baidu.com/item/鸣条之战</t>
         </is>
       </c>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>https://www.qulishi.com/renwu/zhonghui/</t>
+          <t>https://baike.baidu.com/item/仲虺/1980675</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
@@ -1447,16 +1447,16 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>• 《尚书·仲虺之诰》: https://baike.baidu.com/item/仲虺之诰
+          <t>• 《尚书·仲虺之诰》: https://baike.baidu.com/item/仲虺/1980675之诰/5892443
 • 《左传·定公元年》: https://baike.baidu.com/item/左传
-• 百度百科：仲虺: https://baike.baidu.com/item/仲虺</t>
+• 百度百科：仲虺: https://baike.baidu.com/item/仲虺/1980675</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>• 《尚书·仲虺之诰》: https://baike.baidu.com/item/仲虺之诰
-• 《史记·殷本纪》: https://www.zgbk.com/char_1958582.html
-• 百度百科：仲虺之诰: https://baike.baidu.com/item/仲虺之诰</t>
+          <t>• 《尚书·仲虺之诰》: https://baike.baidu.com/item/仲虺之诰/5892443
+• 《史记·殷本纪》: https://baike.baidu.com/item/殷本纪
+• 百度百科：仲虺之诰: https://baike.baidu.com/item/仲虺之诰/5892443</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>https://www.qulishi.com/renwu/youshishishouling/</t>
+          <t>https://baike.baidu.com/item/有施氏</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>https://www.qulishi.com/renwu/minshanshiernv/</t>
+          <t>https://baike.baidu.com/item/妺喜</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>https://www.qulishi.com/renwu/feichang/</t>
+          <t>https://baike.baidu.com/item/费昌</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -1594,13 +1594,13 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>• 《史记·殷本纪》: https://www.zgbk.com/char_1958582.html
+          <t>• 《史记·殷本纪》: https://baike.baidu.com/item/殷本纪
 • 百度百科：费昌: https://baike.baidu.com/item/费昌</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>• 《史记·殷本纪》: https://www.zgbk.com/char_1958582.html</t>
+          <t>• 《史记·殷本纪》: https://baike.baidu.com/item/殷本纪</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>https://www.qulishi.com/renwu/zhonggu/</t>
+          <t>https://baike.baidu.com/item/终古</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
@@ -1649,7 +1649,7 @@
         <is>
           <t>• 《吕氏春秋·先识》: https://baike.baidu.com/item/吕氏春秋
 • 百度百科：终古: https://baike.baidu.com/item/终古
-• 夏朝历史综合参考：《史记·夏本纪》: https://www.zgbk.com/char_1958581.html
+• 夏朝历史综合参考：《史记·夏本纪》: https://baike.baidu.com/item/夏本纪
 • 夏商周断代工程: https://baike.baidu.com/item/夏商周断代工程
 • 知乎：夏朝历史专题: https://www.zhihu.com/topic/19550730/hot</t>
         </is>
